--- a/docs/downloads/08/tbl_main_oeuvre_perm_alaotra_tous.xlsx
+++ b/docs/downloads/08/tbl_main_oeuvre_perm_alaotra_tous.xlsx
@@ -384,7 +384,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Alaotra - Ambatoharanana</t>
+          <t>Ambatoharanana</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -402,7 +402,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Alaotra - Ambatoharanana</t>
+          <t>Ambatoharanana</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -423,7 +423,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Alaotra - Ambatomanga</t>
+          <t>Ambatomanga</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -441,7 +441,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Alaotra - Ambatomanga</t>
+          <t>Ambatomanga</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -462,7 +462,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Alaotra - Ambatomanga</t>
+          <t>Ambatomanga</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -480,7 +480,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Alaotra - Ambatomanga</t>
+          <t>Ambatomanga</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -498,7 +498,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Alaotra - Ambatomanga</t>
+          <t>Ambatomanga</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -516,7 +516,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Alaotra - Ambodivoara</t>
+          <t>Ambodivoara</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -534,7 +534,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Alaotra - Ambodivoara</t>
+          <t>Ambodivoara</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -552,7 +552,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Alaotra - Ambodivoara</t>
+          <t>Ambodivoara</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -570,7 +570,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Alaotra - Ambodivoara</t>
+          <t>Ambodivoara</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -588,7 +588,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Alaotra - Ambodivoara</t>
+          <t>Ambodivoara</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -606,7 +606,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Alaotra - Ambohidrony</t>
+          <t>Ambohidrony</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -627,7 +627,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Alaotra - Ambohidrony</t>
+          <t>Ambohidrony</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -648,7 +648,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Alaotra - Ambohidrony</t>
+          <t>Ambohidrony</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -666,7 +666,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Alaotra - Ambohidrony</t>
+          <t>Ambohidrony</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -687,7 +687,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Alaotra - Ambohidrony</t>
+          <t>Ambohidrony</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -705,7 +705,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Alaotra - Analamiranga</t>
+          <t>Analamiranga</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -723,7 +723,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Alaotra - Analamiranga</t>
+          <t>Analamiranga</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -741,7 +741,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Alaotra - Analamiranga</t>
+          <t>Analamiranga</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -759,7 +759,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Alaotra - Analamiranga</t>
+          <t>Analamiranga</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -780,7 +780,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Alaotra - Avaradrano</t>
+          <t>Avaradrano</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -801,7 +801,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Alaotra - Avaradrano</t>
+          <t>Avaradrano</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -822,7 +822,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Alaotra - Avaradrano</t>
+          <t>Avaradrano</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -843,7 +843,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Alaotra - Avaradrano</t>
+          <t>Avaradrano</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -864,7 +864,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Alaotra - Feramanga Atsimo</t>
+          <t>Feramanga Atsimo</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -885,7 +885,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Alaotra - Feramanga Atsimo</t>
+          <t>Feramanga Atsimo</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -903,7 +903,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Alaotra - Feramanga Atsimo</t>
+          <t>Feramanga Atsimo</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -921,7 +921,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Alaotra - Feramanga Atsimo</t>
+          <t>Feramanga Atsimo</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -939,7 +939,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Alaotra - Mangabe</t>
+          <t>Mangabe</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -960,7 +960,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Alaotra - Mangabe</t>
+          <t>Mangabe</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -981,7 +981,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Alaotra - Mangabe</t>
+          <t>Mangabe</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1002,7 +1002,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Alaotra - Mangabe</t>
+          <t>Mangabe</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1023,7 +1023,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Alaotra - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1044,7 +1044,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Alaotra - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1065,7 +1065,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Alaotra - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1086,7 +1086,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Alaotra - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1107,7 +1107,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Alaotra - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
